--- a/Data_Testing_100_Siswa.xlsx
+++ b/Data_Testing_100_Siswa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Data Testing" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,1431 +397,819 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D101"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nama Lengkap</v>
+        <v>nis</v>
       </c>
       <c r="B1" t="str">
-        <v>NPM/NIS</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Kode Kelas</v>
+        <v>newClassCode</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Siswa Tester 001</v>
+        <v>2024001</v>
       </c>
       <c r="B2" t="str">
-        <v>9900001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>siswa.test001@example.com</v>
-      </c>
-      <c r="D2" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Siswa Tester 002</v>
+        <v>2024002</v>
       </c>
       <c r="B3" t="str">
-        <v>9900002</v>
-      </c>
-      <c r="C3" t="str">
-        <v>siswa.test002@example.com</v>
-      </c>
-      <c r="D3" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Siswa Tester 003</v>
+        <v>2024003</v>
       </c>
       <c r="B4" t="str">
-        <v>9900003</v>
-      </c>
-      <c r="C4" t="str">
-        <v>siswa.test003@example.com</v>
-      </c>
-      <c r="D4" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Siswa Tester 004</v>
+        <v>2024004</v>
       </c>
       <c r="B5" t="str">
-        <v>9900004</v>
-      </c>
-      <c r="C5" t="str">
-        <v>siswa.test004@example.com</v>
-      </c>
-      <c r="D5" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Siswa Tester 005</v>
+        <v>2024005</v>
       </c>
       <c r="B6" t="str">
-        <v>9900005</v>
-      </c>
-      <c r="C6" t="str">
-        <v>siswa.test005@example.com</v>
-      </c>
-      <c r="D6" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Siswa Tester 006</v>
+        <v>2024006</v>
       </c>
       <c r="B7" t="str">
-        <v>9900006</v>
-      </c>
-      <c r="C7" t="str">
-        <v>siswa.test006@example.com</v>
-      </c>
-      <c r="D7" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Siswa Tester 007</v>
+        <v>2024007</v>
       </c>
       <c r="B8" t="str">
-        <v>9900007</v>
-      </c>
-      <c r="C8" t="str">
-        <v>siswa.test007@example.com</v>
-      </c>
-      <c r="D8" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Siswa Tester 008</v>
+        <v>2024008</v>
       </c>
       <c r="B9" t="str">
-        <v>9900008</v>
-      </c>
-      <c r="C9" t="str">
-        <v>siswa.test008@example.com</v>
-      </c>
-      <c r="D9" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Siswa Tester 009</v>
+        <v>2024009</v>
       </c>
       <c r="B10" t="str">
-        <v>9900009</v>
-      </c>
-      <c r="C10" t="str">
-        <v>siswa.test009@example.com</v>
-      </c>
-      <c r="D10" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Siswa Tester 010</v>
+        <v>2024010</v>
       </c>
       <c r="B11" t="str">
-        <v>9900010</v>
-      </c>
-      <c r="C11" t="str">
-        <v>siswa.test010@example.com</v>
-      </c>
-      <c r="D11" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Siswa Tester 011</v>
+        <v>2024011</v>
       </c>
       <c r="B12" t="str">
-        <v>9900011</v>
-      </c>
-      <c r="C12" t="str">
-        <v>siswa.test011@example.com</v>
-      </c>
-      <c r="D12" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Siswa Tester 012</v>
+        <v>2024012</v>
       </c>
       <c r="B13" t="str">
-        <v>9900012</v>
-      </c>
-      <c r="C13" t="str">
-        <v>siswa.test012@example.com</v>
-      </c>
-      <c r="D13" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Siswa Tester 013</v>
+        <v>2024013</v>
       </c>
       <c r="B14" t="str">
-        <v>9900013</v>
-      </c>
-      <c r="C14" t="str">
-        <v>siswa.test013@example.com</v>
-      </c>
-      <c r="D14" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Siswa Tester 014</v>
+        <v>2024014</v>
       </c>
       <c r="B15" t="str">
-        <v>9900014</v>
-      </c>
-      <c r="C15" t="str">
-        <v>siswa.test014@example.com</v>
-      </c>
-      <c r="D15" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Siswa Tester 015</v>
+        <v>2024015</v>
       </c>
       <c r="B16" t="str">
-        <v>9900015</v>
-      </c>
-      <c r="C16" t="str">
-        <v>siswa.test015@example.com</v>
-      </c>
-      <c r="D16" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Siswa Tester 016</v>
+        <v>2024016</v>
       </c>
       <c r="B17" t="str">
-        <v>9900016</v>
-      </c>
-      <c r="C17" t="str">
-        <v>siswa.test016@example.com</v>
-      </c>
-      <c r="D17" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Siswa Tester 017</v>
+        <v>2024017</v>
       </c>
       <c r="B18" t="str">
-        <v>9900017</v>
-      </c>
-      <c r="C18" t="str">
-        <v>siswa.test017@example.com</v>
-      </c>
-      <c r="D18" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Siswa Tester 018</v>
+        <v>2024018</v>
       </c>
       <c r="B19" t="str">
-        <v>9900018</v>
-      </c>
-      <c r="C19" t="str">
-        <v>siswa.test018@example.com</v>
-      </c>
-      <c r="D19" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Siswa Tester 019</v>
+        <v>2024019</v>
       </c>
       <c r="B20" t="str">
-        <v>9900019</v>
-      </c>
-      <c r="C20" t="str">
-        <v>siswa.test019@example.com</v>
-      </c>
-      <c r="D20" t="str">
-        <v>10-B</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Siswa Tester 020</v>
+        <v>2024020</v>
       </c>
       <c r="B21" t="str">
-        <v>9900020</v>
-      </c>
-      <c r="C21" t="str">
-        <v>siswa.test020@example.com</v>
-      </c>
-      <c r="D21" t="str">
-        <v>10-A</v>
+        <v>11A</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Siswa Tester 021</v>
+        <v>2024021</v>
       </c>
       <c r="B22" t="str">
-        <v>9900021</v>
-      </c>
-      <c r="C22" t="str">
-        <v>siswa.test021@example.com</v>
-      </c>
-      <c r="D22" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Siswa Tester 022</v>
+        <v>2024022</v>
       </c>
       <c r="B23" t="str">
-        <v>9900022</v>
-      </c>
-      <c r="C23" t="str">
-        <v>siswa.test022@example.com</v>
-      </c>
-      <c r="D23" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Siswa Tester 023</v>
+        <v>2024023</v>
       </c>
       <c r="B24" t="str">
-        <v>9900023</v>
-      </c>
-      <c r="C24" t="str">
-        <v>siswa.test023@example.com</v>
-      </c>
-      <c r="D24" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Siswa Tester 024</v>
+        <v>2024024</v>
       </c>
       <c r="B25" t="str">
-        <v>9900024</v>
-      </c>
-      <c r="C25" t="str">
-        <v>siswa.test024@example.com</v>
-      </c>
-      <c r="D25" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Siswa Tester 025</v>
+        <v>2024025</v>
       </c>
       <c r="B26" t="str">
-        <v>9900025</v>
-      </c>
-      <c r="C26" t="str">
-        <v>siswa.test025@example.com</v>
-      </c>
-      <c r="D26" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Siswa Tester 026</v>
+        <v>2024026</v>
       </c>
       <c r="B27" t="str">
-        <v>9900026</v>
-      </c>
-      <c r="C27" t="str">
-        <v>siswa.test026@example.com</v>
-      </c>
-      <c r="D27" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Siswa Tester 027</v>
+        <v>2024027</v>
       </c>
       <c r="B28" t="str">
-        <v>9900027</v>
-      </c>
-      <c r="C28" t="str">
-        <v>siswa.test027@example.com</v>
-      </c>
-      <c r="D28" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Siswa Tester 028</v>
+        <v>2024028</v>
       </c>
       <c r="B29" t="str">
-        <v>9900028</v>
-      </c>
-      <c r="C29" t="str">
-        <v>siswa.test028@example.com</v>
-      </c>
-      <c r="D29" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Siswa Tester 029</v>
+        <v>2024029</v>
       </c>
       <c r="B30" t="str">
-        <v>9900029</v>
-      </c>
-      <c r="C30" t="str">
-        <v>siswa.test029@example.com</v>
-      </c>
-      <c r="D30" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Siswa Tester 030</v>
+        <v>2024030</v>
       </c>
       <c r="B31" t="str">
-        <v>9900030</v>
-      </c>
-      <c r="C31" t="str">
-        <v>siswa.test030@example.com</v>
-      </c>
-      <c r="D31" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Siswa Tester 031</v>
+        <v>2024031</v>
       </c>
       <c r="B32" t="str">
-        <v>9900031</v>
-      </c>
-      <c r="C32" t="str">
-        <v>siswa.test031@example.com</v>
-      </c>
-      <c r="D32" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Siswa Tester 032</v>
+        <v>2024032</v>
       </c>
       <c r="B33" t="str">
-        <v>9900032</v>
-      </c>
-      <c r="C33" t="str">
-        <v>siswa.test032@example.com</v>
-      </c>
-      <c r="D33" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Siswa Tester 033</v>
+        <v>2024033</v>
       </c>
       <c r="B34" t="str">
-        <v>9900033</v>
-      </c>
-      <c r="C34" t="str">
-        <v>siswa.test033@example.com</v>
-      </c>
-      <c r="D34" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Siswa Tester 034</v>
+        <v>2024034</v>
       </c>
       <c r="B35" t="str">
-        <v>9900034</v>
-      </c>
-      <c r="C35" t="str">
-        <v>siswa.test034@example.com</v>
-      </c>
-      <c r="D35" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Siswa Tester 035</v>
+        <v>2024035</v>
       </c>
       <c r="B36" t="str">
-        <v>9900035</v>
-      </c>
-      <c r="C36" t="str">
-        <v>siswa.test035@example.com</v>
-      </c>
-      <c r="D36" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Siswa Tester 036</v>
+        <v>2024036</v>
       </c>
       <c r="B37" t="str">
-        <v>9900036</v>
-      </c>
-      <c r="C37" t="str">
-        <v>siswa.test036@example.com</v>
-      </c>
-      <c r="D37" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Siswa Tester 037</v>
+        <v>2024037</v>
       </c>
       <c r="B38" t="str">
-        <v>9900037</v>
-      </c>
-      <c r="C38" t="str">
-        <v>siswa.test037@example.com</v>
-      </c>
-      <c r="D38" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Siswa Tester 038</v>
+        <v>2024038</v>
       </c>
       <c r="B39" t="str">
-        <v>9900038</v>
-      </c>
-      <c r="C39" t="str">
-        <v>siswa.test038@example.com</v>
-      </c>
-      <c r="D39" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Siswa Tester 039</v>
+        <v>2024039</v>
       </c>
       <c r="B40" t="str">
-        <v>9900039</v>
-      </c>
-      <c r="C40" t="str">
-        <v>siswa.test039@example.com</v>
-      </c>
-      <c r="D40" t="str">
-        <v>10-B</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Siswa Tester 040</v>
+        <v>2024040</v>
       </c>
       <c r="B41" t="str">
-        <v>9900040</v>
-      </c>
-      <c r="C41" t="str">
-        <v>siswa.test040@example.com</v>
-      </c>
-      <c r="D41" t="str">
-        <v>10-A</v>
+        <v>11B</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Siswa Tester 041</v>
+        <v>2024041</v>
       </c>
       <c r="B42" t="str">
-        <v>9900041</v>
-      </c>
-      <c r="C42" t="str">
-        <v>siswa.test041@example.com</v>
-      </c>
-      <c r="D42" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Siswa Tester 042</v>
+        <v>2024042</v>
       </c>
       <c r="B43" t="str">
-        <v>9900042</v>
-      </c>
-      <c r="C43" t="str">
-        <v>siswa.test042@example.com</v>
-      </c>
-      <c r="D43" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Siswa Tester 043</v>
+        <v>2024043</v>
       </c>
       <c r="B44" t="str">
-        <v>9900043</v>
-      </c>
-      <c r="C44" t="str">
-        <v>siswa.test043@example.com</v>
-      </c>
-      <c r="D44" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Siswa Tester 044</v>
+        <v>2024044</v>
       </c>
       <c r="B45" t="str">
-        <v>9900044</v>
-      </c>
-      <c r="C45" t="str">
-        <v>siswa.test044@example.com</v>
-      </c>
-      <c r="D45" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Siswa Tester 045</v>
+        <v>2024045</v>
       </c>
       <c r="B46" t="str">
-        <v>9900045</v>
-      </c>
-      <c r="C46" t="str">
-        <v>siswa.test045@example.com</v>
-      </c>
-      <c r="D46" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Siswa Tester 046</v>
+        <v>2024046</v>
       </c>
       <c r="B47" t="str">
-        <v>9900046</v>
-      </c>
-      <c r="C47" t="str">
-        <v>siswa.test046@example.com</v>
-      </c>
-      <c r="D47" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Siswa Tester 047</v>
+        <v>2024047</v>
       </c>
       <c r="B48" t="str">
-        <v>9900047</v>
-      </c>
-      <c r="C48" t="str">
-        <v>siswa.test047@example.com</v>
-      </c>
-      <c r="D48" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Siswa Tester 048</v>
+        <v>2024048</v>
       </c>
       <c r="B49" t="str">
-        <v>9900048</v>
-      </c>
-      <c r="C49" t="str">
-        <v>siswa.test048@example.com</v>
-      </c>
-      <c r="D49" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Siswa Tester 049</v>
+        <v>2024049</v>
       </c>
       <c r="B50" t="str">
-        <v>9900049</v>
-      </c>
-      <c r="C50" t="str">
-        <v>siswa.test049@example.com</v>
-      </c>
-      <c r="D50" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Siswa Tester 050</v>
+        <v>2024050</v>
       </c>
       <c r="B51" t="str">
-        <v>9900050</v>
-      </c>
-      <c r="C51" t="str">
-        <v>siswa.test050@example.com</v>
-      </c>
-      <c r="D51" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Siswa Tester 051</v>
+        <v>2024051</v>
       </c>
       <c r="B52" t="str">
-        <v>9900051</v>
-      </c>
-      <c r="C52" t="str">
-        <v>siswa.test051@example.com</v>
-      </c>
-      <c r="D52" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Siswa Tester 052</v>
+        <v>2024052</v>
       </c>
       <c r="B53" t="str">
-        <v>9900052</v>
-      </c>
-      <c r="C53" t="str">
-        <v>siswa.test052@example.com</v>
-      </c>
-      <c r="D53" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Siswa Tester 053</v>
+        <v>2024053</v>
       </c>
       <c r="B54" t="str">
-        <v>9900053</v>
-      </c>
-      <c r="C54" t="str">
-        <v>siswa.test053@example.com</v>
-      </c>
-      <c r="D54" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Siswa Tester 054</v>
+        <v>2024054</v>
       </c>
       <c r="B55" t="str">
-        <v>9900054</v>
-      </c>
-      <c r="C55" t="str">
-        <v>siswa.test054@example.com</v>
-      </c>
-      <c r="D55" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Siswa Tester 055</v>
+        <v>2024055</v>
       </c>
       <c r="B56" t="str">
-        <v>9900055</v>
-      </c>
-      <c r="C56" t="str">
-        <v>siswa.test055@example.com</v>
-      </c>
-      <c r="D56" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Siswa Tester 056</v>
+        <v>2024056</v>
       </c>
       <c r="B57" t="str">
-        <v>9900056</v>
-      </c>
-      <c r="C57" t="str">
-        <v>siswa.test056@example.com</v>
-      </c>
-      <c r="D57" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Siswa Tester 057</v>
+        <v>2024057</v>
       </c>
       <c r="B58" t="str">
-        <v>9900057</v>
-      </c>
-      <c r="C58" t="str">
-        <v>siswa.test057@example.com</v>
-      </c>
-      <c r="D58" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Siswa Tester 058</v>
+        <v>2024058</v>
       </c>
       <c r="B59" t="str">
-        <v>9900058</v>
-      </c>
-      <c r="C59" t="str">
-        <v>siswa.test058@example.com</v>
-      </c>
-      <c r="D59" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Siswa Tester 059</v>
+        <v>2024059</v>
       </c>
       <c r="B60" t="str">
-        <v>9900059</v>
-      </c>
-      <c r="C60" t="str">
-        <v>siswa.test059@example.com</v>
-      </c>
-      <c r="D60" t="str">
-        <v>10-B</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Siswa Tester 060</v>
+        <v>2024060</v>
       </c>
       <c r="B61" t="str">
-        <v>9900060</v>
-      </c>
-      <c r="C61" t="str">
-        <v>siswa.test060@example.com</v>
-      </c>
-      <c r="D61" t="str">
-        <v>10-A</v>
+        <v>12A</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Siswa Tester 061</v>
+        <v>2024061</v>
       </c>
       <c r="B62" t="str">
-        <v>9900061</v>
-      </c>
-      <c r="C62" t="str">
-        <v>siswa.test061@example.com</v>
-      </c>
-      <c r="D62" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Siswa Tester 062</v>
+        <v>2024062</v>
       </c>
       <c r="B63" t="str">
-        <v>9900062</v>
-      </c>
-      <c r="C63" t="str">
-        <v>siswa.test062@example.com</v>
-      </c>
-      <c r="D63" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Siswa Tester 063</v>
+        <v>2024063</v>
       </c>
       <c r="B64" t="str">
-        <v>9900063</v>
-      </c>
-      <c r="C64" t="str">
-        <v>siswa.test063@example.com</v>
-      </c>
-      <c r="D64" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Siswa Tester 064</v>
+        <v>2024064</v>
       </c>
       <c r="B65" t="str">
-        <v>9900064</v>
-      </c>
-      <c r="C65" t="str">
-        <v>siswa.test064@example.com</v>
-      </c>
-      <c r="D65" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Siswa Tester 065</v>
+        <v>2024065</v>
       </c>
       <c r="B66" t="str">
-        <v>9900065</v>
-      </c>
-      <c r="C66" t="str">
-        <v>siswa.test065@example.com</v>
-      </c>
-      <c r="D66" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Siswa Tester 066</v>
+        <v>2024066</v>
       </c>
       <c r="B67" t="str">
-        <v>9900066</v>
-      </c>
-      <c r="C67" t="str">
-        <v>siswa.test066@example.com</v>
-      </c>
-      <c r="D67" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Siswa Tester 067</v>
+        <v>2024067</v>
       </c>
       <c r="B68" t="str">
-        <v>9900067</v>
-      </c>
-      <c r="C68" t="str">
-        <v>siswa.test067@example.com</v>
-      </c>
-      <c r="D68" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Siswa Tester 068</v>
+        <v>2024068</v>
       </c>
       <c r="B69" t="str">
-        <v>9900068</v>
-      </c>
-      <c r="C69" t="str">
-        <v>siswa.test068@example.com</v>
-      </c>
-      <c r="D69" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Siswa Tester 069</v>
+        <v>2024069</v>
       </c>
       <c r="B70" t="str">
-        <v>9900069</v>
-      </c>
-      <c r="C70" t="str">
-        <v>siswa.test069@example.com</v>
-      </c>
-      <c r="D70" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Siswa Tester 070</v>
+        <v>2024070</v>
       </c>
       <c r="B71" t="str">
-        <v>9900070</v>
-      </c>
-      <c r="C71" t="str">
-        <v>siswa.test070@example.com</v>
-      </c>
-      <c r="D71" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Siswa Tester 071</v>
+        <v>2024071</v>
       </c>
       <c r="B72" t="str">
-        <v>9900071</v>
-      </c>
-      <c r="C72" t="str">
-        <v>siswa.test071@example.com</v>
-      </c>
-      <c r="D72" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Siswa Tester 072</v>
+        <v>2024072</v>
       </c>
       <c r="B73" t="str">
-        <v>9900072</v>
-      </c>
-      <c r="C73" t="str">
-        <v>siswa.test072@example.com</v>
-      </c>
-      <c r="D73" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Siswa Tester 073</v>
+        <v>2024073</v>
       </c>
       <c r="B74" t="str">
-        <v>9900073</v>
-      </c>
-      <c r="C74" t="str">
-        <v>siswa.test073@example.com</v>
-      </c>
-      <c r="D74" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Siswa Tester 074</v>
+        <v>2024074</v>
       </c>
       <c r="B75" t="str">
-        <v>9900074</v>
-      </c>
-      <c r="C75" t="str">
-        <v>siswa.test074@example.com</v>
-      </c>
-      <c r="D75" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Siswa Tester 075</v>
+        <v>2024075</v>
       </c>
       <c r="B76" t="str">
-        <v>9900075</v>
-      </c>
-      <c r="C76" t="str">
-        <v>siswa.test075@example.com</v>
-      </c>
-      <c r="D76" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Siswa Tester 076</v>
+        <v>2024076</v>
       </c>
       <c r="B77" t="str">
-        <v>9900076</v>
-      </c>
-      <c r="C77" t="str">
-        <v>siswa.test076@example.com</v>
-      </c>
-      <c r="D77" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Siswa Tester 077</v>
+        <v>2024077</v>
       </c>
       <c r="B78" t="str">
-        <v>9900077</v>
-      </c>
-      <c r="C78" t="str">
-        <v>siswa.test077@example.com</v>
-      </c>
-      <c r="D78" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Siswa Tester 078</v>
+        <v>2024078</v>
       </c>
       <c r="B79" t="str">
-        <v>9900078</v>
-      </c>
-      <c r="C79" t="str">
-        <v>siswa.test078@example.com</v>
-      </c>
-      <c r="D79" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Siswa Tester 079</v>
+        <v>2024079</v>
       </c>
       <c r="B80" t="str">
-        <v>9900079</v>
-      </c>
-      <c r="C80" t="str">
-        <v>siswa.test079@example.com</v>
-      </c>
-      <c r="D80" t="str">
-        <v>10-B</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Siswa Tester 080</v>
+        <v>2024080</v>
       </c>
       <c r="B81" t="str">
-        <v>9900080</v>
-      </c>
-      <c r="C81" t="str">
-        <v>siswa.test080@example.com</v>
-      </c>
-      <c r="D81" t="str">
-        <v>10-A</v>
+        <v>12B</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Siswa Tester 081</v>
+        <v>2024081</v>
       </c>
       <c r="B82" t="str">
-        <v>9900081</v>
-      </c>
-      <c r="C82" t="str">
-        <v>siswa.test081@example.com</v>
-      </c>
-      <c r="D82" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Siswa Tester 082</v>
+        <v>2024082</v>
       </c>
       <c r="B83" t="str">
-        <v>9900082</v>
-      </c>
-      <c r="C83" t="str">
-        <v>siswa.test082@example.com</v>
-      </c>
-      <c r="D83" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Siswa Tester 083</v>
+        <v>2024083</v>
       </c>
       <c r="B84" t="str">
-        <v>9900083</v>
-      </c>
-      <c r="C84" t="str">
-        <v>siswa.test083@example.com</v>
-      </c>
-      <c r="D84" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Siswa Tester 084</v>
+        <v>2024084</v>
       </c>
       <c r="B85" t="str">
-        <v>9900084</v>
-      </c>
-      <c r="C85" t="str">
-        <v>siswa.test084@example.com</v>
-      </c>
-      <c r="D85" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Siswa Tester 085</v>
+        <v>2024085</v>
       </c>
       <c r="B86" t="str">
-        <v>9900085</v>
-      </c>
-      <c r="C86" t="str">
-        <v>siswa.test085@example.com</v>
-      </c>
-      <c r="D86" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Siswa Tester 086</v>
+        <v>2024086</v>
       </c>
       <c r="B87" t="str">
-        <v>9900086</v>
-      </c>
-      <c r="C87" t="str">
-        <v>siswa.test086@example.com</v>
-      </c>
-      <c r="D87" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Siswa Tester 087</v>
+        <v>2024087</v>
       </c>
       <c r="B88" t="str">
-        <v>9900087</v>
-      </c>
-      <c r="C88" t="str">
-        <v>siswa.test087@example.com</v>
-      </c>
-      <c r="D88" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Siswa Tester 088</v>
+        <v>2024088</v>
       </c>
       <c r="B89" t="str">
-        <v>9900088</v>
-      </c>
-      <c r="C89" t="str">
-        <v>siswa.test088@example.com</v>
-      </c>
-      <c r="D89" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Siswa Tester 089</v>
+        <v>2024089</v>
       </c>
       <c r="B90" t="str">
-        <v>9900089</v>
-      </c>
-      <c r="C90" t="str">
-        <v>siswa.test089@example.com</v>
-      </c>
-      <c r="D90" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Siswa Tester 090</v>
+        <v>2024090</v>
       </c>
       <c r="B91" t="str">
-        <v>9900090</v>
-      </c>
-      <c r="C91" t="str">
-        <v>siswa.test090@example.com</v>
-      </c>
-      <c r="D91" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Siswa Tester 091</v>
+        <v>2024091</v>
       </c>
       <c r="B92" t="str">
-        <v>9900091</v>
-      </c>
-      <c r="C92" t="str">
-        <v>siswa.test091@example.com</v>
-      </c>
-      <c r="D92" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Siswa Tester 092</v>
+        <v>2024092</v>
       </c>
       <c r="B93" t="str">
-        <v>9900092</v>
-      </c>
-      <c r="C93" t="str">
-        <v>siswa.test092@example.com</v>
-      </c>
-      <c r="D93" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Siswa Tester 093</v>
+        <v>2024093</v>
       </c>
       <c r="B94" t="str">
-        <v>9900093</v>
-      </c>
-      <c r="C94" t="str">
-        <v>siswa.test093@example.com</v>
-      </c>
-      <c r="D94" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Siswa Tester 094</v>
+        <v>2024094</v>
       </c>
       <c r="B95" t="str">
-        <v>9900094</v>
-      </c>
-      <c r="C95" t="str">
-        <v>siswa.test094@example.com</v>
-      </c>
-      <c r="D95" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Siswa Tester 095</v>
+        <v>2024095</v>
       </c>
       <c r="B96" t="str">
-        <v>9900095</v>
-      </c>
-      <c r="C96" t="str">
-        <v>siswa.test095@example.com</v>
-      </c>
-      <c r="D96" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Siswa Tester 096</v>
+        <v>2024096</v>
       </c>
       <c r="B97" t="str">
-        <v>9900096</v>
-      </c>
-      <c r="C97" t="str">
-        <v>siswa.test096@example.com</v>
-      </c>
-      <c r="D97" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Siswa Tester 097</v>
+        <v>2024097</v>
       </c>
       <c r="B98" t="str">
-        <v>9900097</v>
-      </c>
-      <c r="C98" t="str">
-        <v>siswa.test097@example.com</v>
-      </c>
-      <c r="D98" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Siswa Tester 098</v>
+        <v>2024098</v>
       </c>
       <c r="B99" t="str">
-        <v>9900098</v>
-      </c>
-      <c r="C99" t="str">
-        <v>siswa.test098@example.com</v>
-      </c>
-      <c r="D99" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Siswa Tester 099</v>
+        <v>2024099</v>
       </c>
       <c r="B100" t="str">
-        <v>9900099</v>
-      </c>
-      <c r="C100" t="str">
-        <v>siswa.test099@example.com</v>
-      </c>
-      <c r="D100" t="str">
-        <v>10-B</v>
+        <v>GRADUATED</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Siswa Tester 100</v>
+        <v>2024100</v>
       </c>
       <c r="B101" t="str">
-        <v>9900100</v>
-      </c>
-      <c r="C101" t="str">
-        <v>siswa.test100@example.com</v>
-      </c>
-      <c r="D101" t="str">
-        <v>10-A</v>
+        <v>GRADUATED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B101"/>
   </ignoredErrors>
 </worksheet>
 </file>